--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Évènement documenté</t>
+    <t>Modèle métier - Évènement documenté</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T10:03:58+00:00</t>
+    <t>2025-04-22T14:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Évènement (acte, traitement, diagnostic, etc…) décrit dans le document.Il y a au minimum une occurrence de cet élément pour décrire l'évènement principal avec obligatoirement une date de début et un exécutant.</t>
+    <t>Évènement (acte, traitement, diagnostic, etc…) décrit dans le document. Il y a au minimum une occurrence de cet élément pour décrire l'évènement principal avec obligatoirement une date de début et un exécutant.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -234,7 +234,7 @@
     <t/>
   </si>
   <si>
-    <t>0</t>
+    <t>1</t>
   </si>
   <si>
     <t>*</t>
@@ -247,6 +247,9 @@
     <t>Base</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Evenement.identifiantEvenement</t>
   </si>
   <si>
@@ -254,20 +257,27 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l’évènement documenté .</t>
+    <t>Identifiant de l’évènement documenté. 
+ Obligatoire pour :
+  - une demande d'acte d'imagerie pour porter l'Order Placer Number.
+  - un CR d’imagerie pour porter le studyInstanceUID.
+ Fourni si connu pour :
+  - une prescription pour porter l'identifiant EPU de la prescription.</t>
   </si>
   <si>
     <t>Evenement.codeEvenement</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Code de l’évènement documenté (obligatoire pour une Demande d'actes d'imagerie, un CR d’imagerie, CR d’examen de l’enfant et un document d’expression personnelle du patient/usager).</t>
+    <t>Code de l’évènement documenté.  
+ Obligatoire pour :
+  - une demande d'actes d'imagerie (code LOINC ='55115-0' 'Demande d’actes d’imagerie')
+  - un CR d’imagerie (code LOINC de l'acte d'imagerie),
+  - un CR d’examen de l’enfant (code SNOMED CT ='11429006' 'consultation'),
+  - un document d’expression personnelle du patient/usager (code TRE_A00 'EXP_PATIENT' 'Expression personnelle du patient').</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -293,21 +303,14 @@
     <t>Evenement.codeEvenement.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -373,7 +376,12 @@
     <t>Evenement.codeEvenement.translation</t>
   </si>
   <si>
-    <t>Translation (obligatoire pour un CR d’imagerie et un CR d’examen de l’enfant.</t>
+    <t>Translation. 
+ Obligatoire pour : 
+  - un CR d’imagerie pour indiquer
+   - 1..* la (ou les) modalité(s) d'acquisition,
+   - 1..* la (ou les) région(s) anatomique(s)
+  - un CR d’examen de l’enfant pour indiquer l'examen (jdv-examen-enfant-obligatoire-cisis).</t>
   </si>
   <si>
     <t>Evenement.dateHeureEvenement</t>
@@ -383,43 +391,19 @@
 </t>
   </si>
   <si>
-    <t>Date et heure de l’évènement documenté.</t>
+    <t>Date et heure de début et de fin de l’évènement documenté. 
+  Date de début obligatoire pour l'évènement documenté principal.</t>
   </si>
   <si>
     <t>Evenement.executantEvenement</t>
   </si>
   <si>
-    <t xml:space="preserve">BackboneElement
+    <t xml:space="preserve">Base
 </t>
   </si>
   <si>
-    <t>Exécutant.</t>
-  </si>
-  <si>
-    <t>Evenement.executantEvenement.id</t>
-  </si>
-  <si>
-    <t>Evenement.executantEvenement.extension</t>
-  </si>
-  <si>
-    <t>Evenement.executantEvenement.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
+    <t>Exécutant. 
+  Obligatoire pour l'évènement documenté principal.</t>
   </si>
   <si>
     <t>Evenement.executantEvenement.roleFonctionnel</t>
@@ -439,6 +423,10 @@
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PersonneStructure
 </t>
+  </si>
+  <si>
+    <t>Exécutant. 
+  Le cadre d'exercice est obligatoire pour l'évènement documenté principal.</t>
   </si>
 </sst>
 </file>
@@ -740,43 +728,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ17"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.56640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.56640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.62109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="53.56640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -978,7 +966,7 @@
         <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>74</v>
@@ -992,10 +980,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1003,7 +991,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>74</v>
@@ -1018,13 +1006,13 @@
         <v>72</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1075,10 +1063,10 @@
         <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>74</v>
@@ -1092,10 +1080,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1103,10 +1091,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G4" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
@@ -1175,13 +1163,13 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH4" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>
@@ -1203,10 +1191,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>72</v>
@@ -1278,10 +1266,10 @@
         <v>89</v>
       </c>
       <c r="AG5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH5" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>72</v>
@@ -1299,14 +1287,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
@@ -1318,17 +1306,15 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M6" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>95</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>72</v>
@@ -1365,22 +1351,22 @@
         <v>72</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>99</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>74</v>
@@ -1389,15 +1375,15 @@
         <v>72</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1405,7 +1391,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>74</v>
@@ -1417,22 +1403,22 @@
         <v>72</v>
       </c>
       <c r="J7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="K7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="O7" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>72</v>
@@ -1481,10 +1467,10 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>74</v>
@@ -1498,10 +1484,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1509,11 +1495,11 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H8" t="s" s="2">
         <v>72</v>
       </c>
@@ -1521,22 +1507,22 @@
         <v>72</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="O8" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>72</v>
@@ -1585,13 +1571,13 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>72</v>
@@ -1602,10 +1588,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1613,7 +1599,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>74</v>
@@ -1631,10 +1617,10 @@
         <v>82</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1685,10 +1671,10 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>74</v>
@@ -1702,10 +1688,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1713,11 +1699,11 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H10" t="s" s="2">
         <v>72</v>
       </c>
@@ -1728,13 +1714,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1785,13 +1771,13 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>72</v>
@@ -1802,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1813,10 +1799,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>72</v>
@@ -1828,13 +1814,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1885,27 +1871,27 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1913,11 +1899,11 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G12" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H12" t="s" s="2">
         <v>72</v>
       </c>
@@ -1928,13 +1914,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1985,13 +1971,13 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="AG12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>72</v>
@@ -2002,22 +1988,22 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
       </c>
@@ -2028,17 +2014,15 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>95</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>72</v>
@@ -2075,31 +2059,31 @@
         <v>72</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AH13" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -2111,39 +2095,35 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>127</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>72</v>
       </c>
@@ -2191,318 +2171,18 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T14:43:59+00:00</t>
+    <t>2025-04-23T09:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:14:13+00:00</t>
+    <t>2025-05-19T09:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T09:31:54+00:00</t>
+    <t>2025-05-20T13:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Evenement.xlsx
+++ b/main/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
